--- a/src/evaluation/data/processed/RES_main_model_travel_time_from_sample_to_hospital.xlsx
+++ b/src/evaluation/data/processed/RES_main_model_travel_time_from_sample_to_hospital.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>49.257259</v>
+        <v>49.25726</v>
       </c>
       <c r="F2" t="n">
         <v>6.852541</v>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.276946</v>
+        <v>49.27695</v>
       </c>
       <c r="F3" t="n">
         <v>6.870121</v>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>49.237085</v>
+        <v>49.23709</v>
       </c>
       <c r="F4" t="n">
         <v>6.99259</v>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49.153009</v>
+        <v>49.15301</v>
       </c>
       <c r="F5" t="n">
         <v>7.048336</v>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49.297734</v>
+        <v>49.29773</v>
       </c>
       <c r="F6" t="n">
         <v>7.054714</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49.495769</v>
+        <v>49.49577</v>
       </c>
       <c r="F7" t="n">
         <v>6.596771</v>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49.495769</v>
+        <v>49.49577</v>
       </c>
       <c r="F8" t="n">
         <v>6.596771</v>
@@ -698,13 +698,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>49.457186</v>
+        <v>49.45719</v>
       </c>
       <c r="F9" t="n">
         <v>6.631578</v>
       </c>
       <c r="G9" t="n">
-        <v>11.96</v>
+        <v>11.97</v>
       </c>
       <c r="H9" t="n">
         <v>11.2</v>
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>49.457186</v>
+        <v>49.49195</v>
       </c>
       <c r="F10" t="n">
-        <v>6.631578</v>
+        <v>6.843934</v>
       </c>
       <c r="G10" t="n">
-        <v>24.09</v>
+        <v>17.23</v>
       </c>
       <c r="H10" t="n">
-        <v>15.07</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="11">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>49.537868</v>
+        <v>49.53787</v>
       </c>
       <c r="F11" t="n">
         <v>6.88934</v>
@@ -788,16 +788,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>49.38458637096774</v>
+        <v>49.41257</v>
       </c>
       <c r="F12" t="n">
-        <v>7.006477401341017</v>
+        <v>6.909871</v>
       </c>
       <c r="G12" t="n">
-        <v>6.77</v>
+        <v>18.12</v>
       </c>
       <c r="H12" t="n">
-        <v>4.32</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="13">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>49.38219174401059</v>
+        <v>49.40381</v>
       </c>
       <c r="F13" t="n">
-        <v>7.018256201104354</v>
+        <v>7.107757</v>
       </c>
       <c r="G13" t="n">
-        <v>5.18</v>
+        <v>9.15</v>
       </c>
       <c r="H13" t="n">
-        <v>2.89</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="14">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>49.41435631447364</v>
+        <v>49.40381</v>
       </c>
       <c r="F14" t="n">
-        <v>7.014796099125492</v>
+        <v>7.107757</v>
       </c>
       <c r="G14" t="n">
-        <v>19.75</v>
+        <v>5.73</v>
       </c>
       <c r="H14" t="n">
-        <v>12.23</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="15">
@@ -878,16 +878,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>49.348293</v>
+        <v>49.40381</v>
       </c>
       <c r="F15" t="n">
-        <v>7.185803</v>
+        <v>7.107757</v>
       </c>
       <c r="G15" t="n">
-        <v>13.85</v>
+        <v>10.89</v>
       </c>
       <c r="H15" t="n">
-        <v>10.16</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="16">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>49.454659</v>
+        <v>49.45466</v>
       </c>
       <c r="F16" t="n">
         <v>7.186793</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>49.266127</v>
+        <v>49.26613</v>
       </c>
       <c r="F17" t="n">
         <v>6.68297</v>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>49.328624</v>
+        <v>49.32862</v>
       </c>
       <c r="F18" t="n">
         <v>6.714977</v>
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49.315236</v>
+        <v>49.31524</v>
       </c>
       <c r="F19" t="n">
         <v>6.756487</v>
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>49.36203214971603</v>
+        <v>49.41909</v>
       </c>
       <c r="F20" t="n">
-        <v>6.864420019821734</v>
+        <v>6.88979</v>
       </c>
       <c r="G20" t="n">
-        <v>17.48</v>
+        <v>24.39</v>
       </c>
       <c r="H20" t="n">
-        <v>6.87</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="21">
@@ -1058,16 +1058,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>49.45713451276023</v>
+        <v>49.41909</v>
       </c>
       <c r="F21" t="n">
-        <v>6.953445233091757</v>
+        <v>6.88979</v>
       </c>
       <c r="G21" t="n">
-        <v>9.26</v>
+        <v>11.06</v>
       </c>
       <c r="H21" t="n">
-        <v>6.58</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="22">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>49.153009</v>
+        <v>49.15301</v>
       </c>
       <c r="F22" t="n">
         <v>7.048336</v>
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>49.290552</v>
+        <v>49.26165</v>
       </c>
       <c r="F23" t="n">
-        <v>7.113175</v>
+        <v>7.252301</v>
       </c>
       <c r="G23" t="n">
-        <v>26.42</v>
+        <v>22.38</v>
       </c>
       <c r="H23" t="n">
-        <v>13.56</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="24">
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>49.317756</v>
+        <v>49.26165</v>
       </c>
       <c r="F24" t="n">
-        <v>7.227015</v>
+        <v>7.252301</v>
       </c>
       <c r="G24" t="n">
-        <v>20.75</v>
+        <v>10.46</v>
       </c>
       <c r="H24" t="n">
-        <v>11.5</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="25">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49.317756</v>
+        <v>49.31776</v>
       </c>
       <c r="F25" t="n">
         <v>7.227015</v>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>49.308199</v>
+        <v>49.3082</v>
       </c>
       <c r="F26" t="n">
         <v>7.351777</v>
@@ -1238,16 +1238,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>49.51467432992366</v>
+        <v>49.56781</v>
       </c>
       <c r="F27" t="n">
-        <v>6.989507755822414</v>
+        <v>6.961946</v>
       </c>
       <c r="G27" t="n">
-        <v>10.82</v>
+        <v>11.28</v>
       </c>
       <c r="H27" t="n">
-        <v>6.22</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="28">
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>49.51656664403166</v>
+        <v>49.54908</v>
       </c>
       <c r="F28" t="n">
-        <v>7.004436754091786</v>
+        <v>7.107687</v>
       </c>
       <c r="G28" t="n">
-        <v>20.4</v>
+        <v>16.89</v>
       </c>
       <c r="H28" t="n">
-        <v>2.69</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>49.51656664403166</v>
+        <v>49.54908</v>
       </c>
       <c r="F29" t="n">
-        <v>7.004436754091786</v>
+        <v>7.107687</v>
       </c>
       <c r="G29" t="n">
-        <v>28.2</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>11.47</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="30">
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>49.454659</v>
+        <v>49.54908</v>
       </c>
       <c r="F30" t="n">
-        <v>7.186793</v>
+        <v>7.107687</v>
       </c>
       <c r="G30" t="n">
-        <v>15.19</v>
+        <v>12.1</v>
       </c>
       <c r="H30" t="n">
-        <v>11.82</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="31">
@@ -1358,16 +1358,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>49.454659</v>
+        <v>49.54908</v>
       </c>
       <c r="F31" t="n">
-        <v>7.186793</v>
+        <v>7.107687</v>
       </c>
       <c r="G31" t="n">
-        <v>24.64</v>
+        <v>17.88</v>
       </c>
       <c r="H31" t="n">
-        <v>18.77</v>
+        <v>13.81</v>
       </c>
     </row>
   </sheetData>
